--- a/test/技术工单/输入附件.xlsx
+++ b/test/技术工单/输入附件.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="issues" sheetId="1" r:id="R5cfa66dbb7bc4a2b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="activity" sheetId="2" r:id="R93bf8e9a99f143ea"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="issues" sheetId="1" r:id="R3d1686bff8a94c99"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="activity" sheetId="2" r:id="R683c706c915241e9"/>
   </x:sheets>
 </x:workbook>
 </file>
